--- a/SGC-CKN/Excel/8fbc4c86-e905-42f9-97c2-c4754e82f05e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_PH-86_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/8fbc4c86-e905-42f9-97c2-c4754e82f05e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_PH-86_D800_13-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PH-86</t>
+    <t>P11-86</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/8fbc4c86-e905-42f9-97c2-c4754e82f05e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_PH-86_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/8fbc4c86-e905-42f9-97c2-c4754e82f05e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_PH-86_D800_13-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-86</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
@@ -106,10 +106,13 @@
 12/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:45
@@ -123,7 +126,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">16:15
@@ -137,9 +140,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">05:30
 13/03/2026</t>
   </si>
@@ -151,7 +151,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">07:00
@@ -165,7 +165,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:25
@@ -179,9 +179,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">09:05
 13/03/2026</t>
   </si>
@@ -196,7 +193,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:50
@@ -244,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -310,11 +307,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF164E63"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -327,7 +319,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,11 +384,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -492,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -575,22 +562,13 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1191,24 +1169,24 @@
         <v>5.14</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-1.2</v>
@@ -1226,24 +1204,24 @@
         <v>9.52</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-5.8</v>
@@ -1261,18 +1239,18 @@
         <v>7.2</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>40</v>
@@ -1296,7 +1274,7 @@
         <v>3.51</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1331,7 +1309,7 @@
         <v>10.76</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1366,93 +1344,93 @@
         <v>6</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-39.4</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-45.8</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>0.73</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>6.4</v>
       </c>
       <c r="J17" s="8">
         <v>8.73</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-45.8</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-49.95</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.92</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>4.15</v>
       </c>
       <c r="J18" s="18">
         <v>4.53</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1534,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1547,31 +1525,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1611,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1640,7 +1618,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1669,7 +1647,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1730,22 +1708,22 @@
         <v>47</v>
       </c>
       <c r="D7" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="22">
         <v>-35.9</v>
       </c>
       <c r="F7" s="22">
-        <v>-39.4</v>
+        <v>-45.8</v>
       </c>
       <c r="G7" s="22">
-        <v>0.58</v>
+        <v>1.32</v>
       </c>
       <c r="H7" s="22">
-        <v>3.5</v>
+        <v>9.9</v>
       </c>
       <c r="I7" s="8">
-        <v>6</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1756,82 +1734,53 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-39.4</v>
+        <v>-45.8</v>
       </c>
       <c r="F8" s="25">
-        <v>-45.8</v>
+        <v>-49.95</v>
       </c>
       <c r="G8" s="25">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H8" s="25">
-        <v>6.4</v>
-      </c>
-      <c r="I8" s="8">
-        <v>8.73</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+        <v>4.15</v>
+      </c>
+      <c r="I8" s="18">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="30">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="28">
-        <v>1</v>
-      </c>
-      <c r="E9" s="28">
-        <v>-45.8</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
         <v>-49.95</v>
       </c>
-      <c r="G9" s="28">
-        <v>0.92</v>
-      </c>
-      <c r="H9" s="28">
-        <v>4.15</v>
-      </c>
-      <c r="I9" s="18">
-        <v>4.53</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="33">
-        <v>8</v>
-      </c>
-      <c r="E10" s="33">
-        <v>0</v>
-      </c>
-      <c r="F10" s="33">
-        <v>-49.95</v>
-      </c>
-      <c r="G10" s="33">
+      <c r="G9" s="30">
         <v>7.22</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H9" s="30">
         <v>49.95</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I9" s="30">
         <v>6.92</v>
       </c>
     </row>
